--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -107,6 +107,24 @@
   </si>
   <si>
     <t>19</t>
+  </si>
+  <si>
+    <t>20131748</t>
+  </si>
+  <si>
+    <t>KABEL TIES</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20118156</t>
+  </si>
+  <si>
+    <t>ROLL STRUK LBL BC4X3</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
 </sst>
 </file>
@@ -499,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -697,6 +715,46 @@
         <v>16</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -109,22 +109,13 @@
     <t>19</t>
   </si>
   <si>
-    <t>20131748</t>
-  </si>
-  <si>
-    <t>KABEL TIES</t>
+    <t>20118156</t>
+  </si>
+  <si>
+    <t>ROLL STRUK LBL BC4X3</t>
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>20118156</t>
-  </si>
-  <si>
-    <t>ROLL STRUK LBL BC4X3</t>
-  </si>
-  <si>
-    <t>21</t>
   </si>
 </sst>
 </file>
@@ -517,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -732,26 +723,6 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
   <si>
     <t/>
   </si>
@@ -100,6 +100,15 @@
     <t>17</t>
   </si>
   <si>
+    <t>20136561</t>
+  </si>
+  <si>
+    <t>APRICOT KARET GELANG</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>20054963</t>
   </si>
   <si>
@@ -116,6 +125,15 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>20128131</t>
+  </si>
+  <si>
+    <t>ROLL BUAH SEAL 8CM</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
 </sst>
 </file>
@@ -508,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -686,7 +704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -701,9 +719,6 @@
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -723,6 +738,46 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,30 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
-    <t>20118154</t>
-  </si>
-  <si>
-    <t>ROLL PLASTIK BUAH</t>
+    <t>20118157</t>
+  </si>
+  <si>
+    <t>ROLL STRUK EDC BCA</t>
   </si>
   <si>
     <t>RPOTA</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20118157</t>
-  </si>
-  <si>
-    <t>ROLL STRUK EDC BCA</t>
   </si>
   <si>
     <t>4</t>
@@ -526,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -556,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -572,25 +563,28 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,15 +604,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -627,13 +621,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -649,8 +640,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -665,9 +659,6 @@
       </c>
       <c r="E7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -704,7 +695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -719,6 +710,9 @@
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -738,7 +732,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -758,27 +752,7 @@
         <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -517,17 +517,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="6" width="4" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,8 +548,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -563,11 +571,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -583,11 +591,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -603,7 +611,7 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -624,7 +632,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -640,7 +648,7 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -695,7 +703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -711,11 +719,11 @@
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -731,11 +739,11 @@
       <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -751,7 +759,7 @@
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -517,19 +517,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="5" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,14 +546,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -571,11 +563,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -591,11 +583,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -611,7 +603,7 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -632,7 +624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -648,7 +640,7 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -703,7 +695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -719,11 +711,11 @@
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -739,11 +731,11 @@
       <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -759,7 +751,7 @@
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -28,103 +28,103 @@
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20118158</t>
+  </si>
+  <si>
+    <t>ROLL STRK EDC WDCARD</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20118158</t>
-  </si>
-  <si>
-    <t>ROLL STRK EDC WDCARD</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20118169</t>
   </si>
   <si>
     <t>KERTAS 1 PLY N101</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20118173</t>
+  </si>
+  <si>
+    <t>TL.RAPIA GL 1KG N402</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20118173</t>
-  </si>
-  <si>
-    <t>TL.RAPIA GL 1KG N402</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20131479</t>
   </si>
   <si>
     <t>ROLL STRK EDC MTI</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20131747</t>
+  </si>
+  <si>
+    <t>KARET GELANG</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
-    <t>20131747</t>
-  </si>
-  <si>
-    <t>KARET GELANG</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20136899</t>
   </si>
   <si>
     <t>ROL STRK THERMAL57MM</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20136561</t>
+  </si>
+  <si>
+    <t>APRICOT KARET GELANG</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
-    <t>20136561</t>
-  </si>
-  <si>
-    <t>APRICOT KARET GELANG</t>
+    <t>20054963</t>
+  </si>
+  <si>
+    <t>KNTONG PLST BUAH ROL</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20054963</t>
-  </si>
-  <si>
-    <t>KNTONG PLST BUAH ROL</t>
+    <t>20118156</t>
+  </si>
+  <si>
+    <t>ROLL STRUK LBL BC4X3</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>20118156</t>
-  </si>
-  <si>
-    <t>ROLL STRUK LBL BC4X3</t>
+    <t>20128131</t>
+  </si>
+  <si>
+    <t>ROLL BUAH SEAL 8CM</t>
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>20128131</t>
-  </si>
-  <si>
-    <t>ROLL BUAH SEAL 8CM</t>
-  </si>
-  <si>
-    <t>21</t>
   </si>
 </sst>
 </file>
